--- a/state/ar/run-report-2026-10-27.xlsx
+++ b/state/ar/run-report-2026-10-27.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Detailed Results" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Failures" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Discovery Changes" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Coverage &amp; Plan" state="visible" r:id="rId8"/>
+    <sheet sheetId="2" name="Test Cases" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Detailed Results" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Failures" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Discovery Changes" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Coverage &amp; Plan" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="513">
   <si>
     <t>Metric</t>
   </si>
@@ -71,6 +72,861 @@
     <t>PASS 43 | FAIL 9 | FLAKY 0 | NOT RUN 0</t>
   </si>
   <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Case Description</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تسوّّق حسب الماركة
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-001</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-001, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t>Homepage loaded at HOMEPAGE_BASE_URL (production) + locale path; guest session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-001 ("تسوّّق حسب الماركة").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-001].elements.links</t>
+  </si>
+  <si>
+    <t>All links resolve to a live page matching their href; no console errors or failed navigation requests are introduced.</t>
+  </si>
+  <si>
+    <t>FAIL: [31mTest timeout of 60000ms exceeded.[39m</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-002</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-001, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-001 ("تسوّّق حسب الماركة").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-001].elements.buttons</t>
+  </si>
+  <si>
+    <t>Every button performs its expected action; disabled buttons stay disabled and are not treated as failures.</t>
+  </si>
+  <si>
+    <t>PASS: matches expected</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-003</t>
+  </si>
+  <si>
+    <t>Exercise Next repeatedly to the last slide and confirm it loops or stops correctly; exercise Previous back to the first slide; rapid-click Next/Previous; click any slide CTA/link.</t>
+  </si>
+  <si>
+    <t>Homepage loaded; carousel visible in viewport.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage and scroll the carousel into view.
+2. Click Next N times (N = detected slide/link count) and screenshot each slide.
+3. Click Previous back to the first slide.
+4. Rapid-click Next 5x in quick succession; confirm the carousel settles on a valid, non-blank slide.
+5. Click each pagination indicator (if any) and confirm the matching slide shows.
+6. Click a slide CTA/link where present and confirm navigation (flag any href="#" placeholder as a finding rather than a pass).</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-001].elements.sliders</t>
+  </si>
+  <si>
+    <t>No blank/duplicate slides, no stuck navigation, pagination indicators (if present) reflect the active slide, and CTAs navigate to real destinations.</t>
+  </si>
+  <si>
+    <t>FAIL: TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: [2m - waiting for getByRole('button', { name: /previous/i }).first()[22m [2m - locator resolved to &lt;button type="button" data-role="none" class="slick-arrow slick-prev"&gt; Previous&lt;/button&gt;[22m [2m - attempting click action[22m [2</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-005</t>
+  </si>
+  <si>
+    <t>Enter typical, empty, very long, and special-character values; confirm no crash, no console error, and reasonable UI feedback.</t>
+  </si>
+  <si>
+    <t>Homepage loaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Locate each input in the section.
+2. Type a typical query/value and confirm expected behavior (e.g. search suggestions).
+3. Clear and submit empty; confirm no crash.
+4. Type a very long string (200+ chars) and Unicode/Arabic text; confirm no overflow/crash.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-001].elements.inputs</t>
+  </si>
+  <si>
+    <t>Inputs handle all cases gracefully with no console errors or broken layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عروض الأسبوع
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-022</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-006, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-006 ("عروض الأسبوع").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-006].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-023</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-006, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-006 ("عروض الأسبوع").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-006].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-024</t>
+  </si>
+  <si>
+    <t>Sample 3 representative cards (first, middle, last of the sampled set): verify image loads, name is fully visible (no unexpected clipping), price is present, wishlist toggles, Add to Cart succeeds, and clicking the card navigates to a matching PDP.</t>
+  </si>
+  <si>
+    <t>Homepage loaded; guest session; widget scrolled into view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage and scroll the widget into view.
+2. Pick first/middle/last sampled card.
+3. Assert image is not broken (naturalWidth &gt; 0).
+4. Assert product name is present and not truncated in a way that hides essential info.
+5. Assert a price is displayed.
+6. Click the wishlist control and confirm a visible state change.
+7. Click Add to Cart and confirm a cart-updated confirmation appears.
+8. Click the card and confirm the destination PDP matches the card's product name.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-006].elements.productCards</t>
+  </si>
+  <si>
+    <t>Card content is complete and consistent; wishlist/add-to-cart succeed; PDP navigation lands on the matching product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتجات الأكثر شعبية
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-026</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-007, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-007 ("المنتجات الأكثر شعبية").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-007].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-027</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-007, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-007 ("المنتجات الأكثر شعبية").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-007].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-028</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-007].elements.productCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استكشف جواهرنا الخفية
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-030</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-008, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-008 ("استكشف جواهرنا الخفية").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-008].elements.links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جديد في مجموعتنا
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-032</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-009, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-009 ("جديد في مجموعتنا").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-009].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-033</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-009, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-009 ("جديد في مجموعتنا").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-009].elements.buttons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عروض اس تثنائية💖
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-036</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-010, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-010 ("عروض اس تثنائية💖").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-010].elements.links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتجات على ذوقك
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-038</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-011, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-011 ("منتجات على ذوقك").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-011].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-039</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-011, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-011 ("منتجات على ذوقك").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-011].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-040</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-011].elements.productCards</t>
+  </si>
+  <si>
+    <t>FAIL: Error: No product cards found live for widget originally titled "منتجات على ذوقك" — checked exact text match and the widget in the same document position, neither had any Add to Cart button [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m [</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتجات مناسبة لكل عمر
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-042</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-012, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-012 ("منتجات مناسبة لكل عمر").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-012].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-043</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-012, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-012 ("منتجات مناسبة لكل عمر").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-012].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-044</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-012].elements.productCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نصنع السعادة , نخلق الذكريات
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-046</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-013, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-013 ("نصنع السعادة , نخلق الذكريات").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-013].elements.buttons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⭐ بتقييم 4.7 على قوقل
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-048</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-014, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-014 ("⭐ بتقييم 4.7 على قوقل").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-014].elements.links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تسوق حسب الفئة
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-049</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-019, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-019 ("تسوق حسب الفئة").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-019].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-050</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-019, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-019 ("تسوق حسب الفئة").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-019].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-052</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-019].elements.inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsive
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-053</t>
+  </si>
+  <si>
+    <t>Load the homepage at 1440x900 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 1440x900.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 1440x900.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>No horizontal overflow; all key sections are usable and visually intact at this viewport.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-054</t>
+  </si>
+  <si>
+    <t>Load the homepage at 1920x1080 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 1920x1080.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 1920x1080.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-055</t>
+  </si>
+  <si>
+    <t>Load the homepage at 1024x768 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 1024x768.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 1024x768.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-056</t>
+  </si>
+  <si>
+    <t>Load the homepage at 768x1024 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 768x1024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 768x1024.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-057</t>
+  </si>
+  <si>
+    <t>Load the homepage at 390x844 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 390x844.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 390x844.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-058</t>
+  </si>
+  <si>
+    <t>Load the homepage at 393x852 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 393x852.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 393x852.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-059</t>
+  </si>
+  <si>
+    <t>Load the homepage at 412x915 and check header, hero, category grid, product widgets, footer for layout breakage.</t>
+  </si>
+  <si>
+    <t>Viewport set to 412x915.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set viewport to 412x915.
+2. Load the homepage.
+3. Check for horizontal scroll on body/html.
+4. Screenshot header, hero, first two product widgets, and footer.
+5. Confirm no element overlap or CTA clipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-063</t>
+  </si>
+  <si>
+    <t>Tab through the homepage from the top and confirm a visible focus indicator on every stop; cross-check accessible names against homepage-map.json for blank names.</t>
+  </si>
+  <si>
+    <t>Homepage loaded, desktop viewport.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Press Tab repeatedly from the top of the page and screenshot the focus ring at each header/hero control.
+3. Cross-reference homepage-map.json for interactive elements with an empty accessible name (candidates already flagged: unlabeled logo/cart/menu icon links).
+4. Confirm heading structure is hierarchical (no skipped levels) for the section headings captured in homepage-map.json.</t>
+  </si>
+  <si>
+    <t>state/${LOCALE}/homepage-map.json → any element with name === ""</t>
+  </si>
+  <si>
+    <t>All interactive elements are keyboard-reachable with a visible focus state and a non-empty accessible name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative &amp; edge
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-064</t>
+  </si>
+  <si>
+    <t>Rapid double-click the same CTA, navigate back/forward through a homepage-&gt;PDP-&gt;homepage sequence, and refresh mid-load; confirm no console errors or stuck UI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Double-click "Add to Cart" on a homepage product card in quick succession; confirm no duplicate cart entries and no crash.
+2. Navigate homepage -&gt; a product PDP -&gt; browser Back -&gt; browser Forward; confirm each state renders correctly.
+3. Reload the homepage mid-carousel-animation; confirm it settles into a valid state.
+4. Throttle network to slow 3G (or simulate) and confirm skeleton/loading states appear rather than a blank page.</t>
+  </si>
+  <si>
+    <t>No crashes, duplicate actions, or stuck UI under any of the above; console stays free of new errors.</t>
+  </si>
+  <si>
+    <t>FAIL: Error: Clicking a product card did not navigate away from the homepage (still at https://thekanaa.com/ar-sa/) Back navigation did not return to homepage (at about:blank) — reproduced once; rerun to confirm before filing as a bug [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Console &amp; network health
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-065</t>
+  </si>
+  <si>
+    <t>Load the homepage fresh and classify every console error / failed request as first-party (site code, API, CDN-hosted asset) vs third-party (analytics/ads beacon), then evaluate only the first-party ones as candidate defects.</t>
+  </si>
+  <si>
+    <t>Fresh session, no ad blocker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage with console/network listeners attached from before navigation.
+2. Classify each captured error/failure by host (thekanaa.com and its subdomains, e.g. media-stage.thekanaa.com = first-party; google.com, doubleclick.net, google-analytics.com, merchant-center-analytics.goog = third-party).
+3. For first-party failures only, correlate to the section/element responsible and file as a candidate bug.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → consoleErrors (0 captured), networkFailures (13 captured)</t>
+  </si>
+  <si>
+    <t>Zero first-party console errors or failed first-party requests on a clean homepage load.</t>
+  </si>
+  <si>
+    <t>FAIL: Error: POST https://thekanaa.com/ar-sa/ -&gt; net::ERR_ABORTED GET https://thekanaa.com/ar-sa/backtoschool/?_rsc=P6_Td76J5h7eMe0- -&gt; net::ERR_ABORTED GET https://thekanaa.com/ar-sa/toys-games/cars-vehicles.html?_rsc=P6_Td76J5h7eMe0- -&gt; net::ERR_ABORTED GET https://thekanaa.com/ar-sa/gaming-consoles.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localization
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-066</t>
+  </si>
+  <si>
+    <t>Click the header language switcher ("EN") and confirm the resulting URL and &lt;html dir&gt; attribute match the target locale, with no overflow.</t>
+  </si>
+  <si>
+    <t>Homepage loaded in Arabic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the header language switcher.
+2. Confirm the URL now contains "/en-sa/".
+3. Confirm &lt;html dir="ltr"&gt; (or equivalent) is applied on the destination page.
+4. Confirm no horizontal overflow was introduced by the switch.</t>
+  </si>
+  <si>
+    <t>Header language switcher button (accessible name "EN")</t>
+  </si>
+  <si>
+    <t>Language switcher reliably navigates to the other locale with the correct text direction and no layout breakage.</t>
+  </si>
+  <si>
+    <t>FAIL: Error: URL did not change to the English locale after clicking the switcher (still at https://thekanaa.com/ar-sa/) Expected &lt;html dir="ltr"&gt; after switching to English, got dir="rtl" [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m [32m- Ex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance observation
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-067</t>
+  </si>
+  <si>
+    <t>Measure time-to-first-contentful-paint-equivalent (hero banner visible) and count duplicate network requests to the same endpoint within one page load.</t>
+  </si>
+  <si>
+    <t>Fresh session, no throttling (baseline) then Slow 3G (comparison).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage with network logging enabled.
+2. Record time until the hero carousel controls are interactive.
+3. Group network requests by URL and flag any endpoint called more than once with identical params within the same load.</t>
+  </si>
+  <si>
+    <t>Network log from a full homepage load.</t>
+  </si>
+  <si>
+    <t>No destructive/duplicate-fetch pattern; load reaches an interactive hero within a few seconds on an unthrottled connection. This is an observational check, not a load/stress test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أحدث التقنيات، بأفضل قيمة
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-068</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-002, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-002 ("أحدث التقنيات، بأفضل قيمة").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-002].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-069</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-002, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-002 ("أحدث التقنيات، بأفضل قيمة").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-002].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-070</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-002].elements.productCards</t>
+  </si>
+  <si>
+    <t>FAIL: Error: smoke Add to Cart (sample #0) failed: locator.click: Timeout 5000ms exceeded. Call log: [2m - waiting for getByRole('button', { name: /إضافة إلى السلة/ }).first()[22m [2m - locator — see README "Known site quirks" re: throttling before filing as a bug [2mexpect([22m[31mreceived[39m[2m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أقوى الألعاب، وأفضل العروض
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-072</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-003, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-003 ("أقوى الألعاب، وأفضل العروض").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-003].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-073</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-003, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-003 ("أقوى الألعاب، وأفضل العروض").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-003].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-074</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-003].elements.productCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارتق إلى آيفون 18
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-076</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-004, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-004 ("ارتق إلى آيفون 18").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-004].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-077</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-004, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-004 ("ارتق إلى آيفون 18").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-004].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-078</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-004].elements.productCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أناقة بسيطة، وسحر لا يقاوم.
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-080</t>
+  </si>
+  <si>
+    <t>For each link in section HOME-SEC-AR-005, click it, confirm the resulting URL/page matches the href's intent, then navigate back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-005 ("أناقة بسيطة، وسحر لا يقاوم.").
+3. For each link: assert visible+enabled, click, assert no 4xx/5xx navigation and no new console error, assert back navigation restores the homepage.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-005].elements.links</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-081</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-005, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-005 ("أناقة بسيطة، وسحر لا يقاوم.").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-005].elements.buttons</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-082</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-005].elements.productCards</t>
+  </si>
+  <si>
+    <t>FAIL: Error: No product cards found live for widget originally titled "أناقة بسيطة، وسحر لا يقاوم." — checked exact text match and the widget in the same document position, neither had any Add to Cart button [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تسوق حسب القسم
+Note: Web (Chromium desktop), locale AR, run 2026-10-27</t>
+  </si>
+  <si>
+    <t>TC-HOME-AR-084</t>
+  </si>
+  <si>
+    <t>For each button in section HOME-SEC-AR-016, verify pre-click state, click, and verify the expected UI/state change with no console or network error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load the homepage.
+2. Locate section HOME-SEC-AR-016 ("تسوق حسب القسم").
+3. For each button: assert accessible name is non-empty, assert visible/enabled state matches design intent, click, assert expected state change, assert no new console error.</t>
+  </si>
+  <si>
+    <t>state/ar/homepage-map.json → sections[id=HOME-SEC-AR-016].elements.buttons</t>
+  </si>
+  <si>
     <t>Test case ID</t>
   </si>
   <si>
@@ -107,9 +963,6 @@
     <t>Severity</t>
   </si>
   <si>
-    <t>TC-HOME-AR-002</t>
-  </si>
-  <si>
     <t>تسوّّق حسب الماركة — buttons</t>
   </si>
   <si>
@@ -122,9 +975,6 @@
     <t>7664</t>
   </si>
   <si>
-    <t>TC-HOME-AR-069</t>
-  </si>
-  <si>
     <t>أحدث التقنيات، بأفضل قيمة — buttons</t>
   </si>
   <si>
@@ -134,9 +984,6 @@
     <t>1799</t>
   </si>
   <si>
-    <t>TC-HOME-AR-073</t>
-  </si>
-  <si>
     <t>أقوى الألعاب، وأفضل العروض — buttons</t>
   </si>
   <si>
@@ -146,9 +993,6 @@
     <t>1865</t>
   </si>
   <si>
-    <t>TC-HOME-AR-077</t>
-  </si>
-  <si>
     <t>ارتق إلى آيفون 18 — buttons</t>
   </si>
   <si>
@@ -158,9 +1002,6 @@
     <t>2113</t>
   </si>
   <si>
-    <t>TC-HOME-AR-081</t>
-  </si>
-  <si>
     <t>أناقة بسيطة، وسحر لا يقاوم. — buttons</t>
   </si>
   <si>
@@ -170,9 +1011,6 @@
     <t>2464</t>
   </si>
   <si>
-    <t>TC-HOME-AR-023</t>
-  </si>
-  <si>
     <t>عروض الأسبوع — buttons</t>
   </si>
   <si>
@@ -182,9 +1020,6 @@
     <t>2047</t>
   </si>
   <si>
-    <t>TC-HOME-AR-027</t>
-  </si>
-  <si>
     <t>المنتجات الأكثر شعبية — buttons</t>
   </si>
   <si>
@@ -194,9 +1029,6 @@
     <t>3297</t>
   </si>
   <si>
-    <t>TC-HOME-AR-033</t>
-  </si>
-  <si>
     <t>جديد في مجموعتنا — buttons</t>
   </si>
   <si>
@@ -206,9 +1038,6 @@
     <t>3580</t>
   </si>
   <si>
-    <t>TC-HOME-AR-039</t>
-  </si>
-  <si>
     <t>منتجات على ذوقك — buttons</t>
   </si>
   <si>
@@ -218,9 +1047,6 @@
     <t>3224</t>
   </si>
   <si>
-    <t>TC-HOME-AR-043</t>
-  </si>
-  <si>
     <t>منتجات مناسبة لكل عمر — buttons</t>
   </si>
   <si>
@@ -230,9 +1056,6 @@
     <t>1976</t>
   </si>
   <si>
-    <t>TC-HOME-AR-046</t>
-  </si>
-  <si>
     <t>نصنع السعادة , نخلق الذكريات — buttons</t>
   </si>
   <si>
@@ -242,9 +1065,6 @@
     <t>2607</t>
   </si>
   <si>
-    <t>TC-HOME-AR-084</t>
-  </si>
-  <si>
     <t>تسوق حسب القسم — buttons</t>
   </si>
   <si>
@@ -254,9 +1074,6 @@
     <t>5268</t>
   </si>
   <si>
-    <t>TC-HOME-AR-050</t>
-  </si>
-  <si>
     <t>تسوق حسب الفئة — buttons</t>
   </si>
   <si>
@@ -275,9 +1092,6 @@
     <t>35541</t>
   </si>
   <si>
-    <t>TC-HOME-AR-001</t>
-  </si>
-  <si>
     <t>تسوّّق حسب الماركة — links</t>
   </si>
   <si>
@@ -293,9 +1107,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--0eba8-R-001-—-every-link-resolves-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--0eba8-R-001-—-every-link-resolves-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--0eba8-R-001-—-every-link-resolves-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--0eba8-R-001-—-every-link-resolves-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-068</t>
-  </si>
-  <si>
     <t>أحدث التقنيات، بأفضل قيمة — links</t>
   </si>
   <si>
@@ -305,9 +1116,6 @@
     <t>28586</t>
   </si>
   <si>
-    <t>TC-HOME-AR-072</t>
-  </si>
-  <si>
     <t>أقوى الألعاب، وأفضل العروض — links</t>
   </si>
   <si>
@@ -317,9 +1125,6 @@
     <t>18552</t>
   </si>
   <si>
-    <t>TC-HOME-AR-076</t>
-  </si>
-  <si>
     <t>ارتق إلى آيفون 18 — links</t>
   </si>
   <si>
@@ -329,9 +1134,6 @@
     <t>37047</t>
   </si>
   <si>
-    <t>TC-HOME-AR-080</t>
-  </si>
-  <si>
     <t>أناقة بسيطة، وسحر لا يقاوم. — links</t>
   </si>
   <si>
@@ -341,9 +1143,6 @@
     <t>19788</t>
   </si>
   <si>
-    <t>TC-HOME-AR-022</t>
-  </si>
-  <si>
     <t>عروض الأسبوع — links</t>
   </si>
   <si>
@@ -353,9 +1152,6 @@
     <t>18550</t>
   </si>
   <si>
-    <t>TC-HOME-AR-026</t>
-  </si>
-  <si>
     <t>المنتجات الأكثر شعبية — links</t>
   </si>
   <si>
@@ -365,9 +1161,6 @@
     <t>17209</t>
   </si>
   <si>
-    <t>TC-HOME-AR-030</t>
-  </si>
-  <si>
     <t>استكشف جواهرنا الخفية — links</t>
   </si>
   <si>
@@ -377,9 +1170,6 @@
     <t>1272</t>
   </si>
   <si>
-    <t>TC-HOME-AR-032</t>
-  </si>
-  <si>
     <t>جديد في مجموعتنا — links</t>
   </si>
   <si>
@@ -389,9 +1179,6 @@
     <t>1228</t>
   </si>
   <si>
-    <t>TC-HOME-AR-036</t>
-  </si>
-  <si>
     <t>عروض اس تثنائية💖 — links</t>
   </si>
   <si>
@@ -401,9 +1188,6 @@
     <t>7239</t>
   </si>
   <si>
-    <t>TC-HOME-AR-038</t>
-  </si>
-  <si>
     <t>منتجات على ذوقك — links</t>
   </si>
   <si>
@@ -413,9 +1197,6 @@
     <t>23092</t>
   </si>
   <si>
-    <t>TC-HOME-AR-042</t>
-  </si>
-  <si>
     <t>منتجات مناسبة لكل عمر — links</t>
   </si>
   <si>
@@ -425,9 +1206,6 @@
     <t>51771</t>
   </si>
   <si>
-    <t>TC-HOME-AR-048</t>
-  </si>
-  <si>
     <t>⭐ بتقييم 4.7 على قوقل — links</t>
   </si>
   <si>
@@ -437,9 +1215,6 @@
     <t>1390</t>
   </si>
   <si>
-    <t>TC-HOME-AR-049</t>
-  </si>
-  <si>
     <t>تسوق حسب الفئة — links</t>
   </si>
   <si>
@@ -452,9 +1227,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--408e1-R-020-—-every-link-resolves-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--408e1-R-020-—-every-link-resolves-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--408e1-R-020-—-every-link-resolves-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-links-TC-HOME-AR--408e1-R-020-—-every-link-resolves-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-064</t>
-  </si>
-  <si>
     <t>Negative &amp; edge — interaction robustness</t>
   </si>
   <si>
@@ -473,9 +1245,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-negative-TC-HOME--f0b30-ge-—-interaction-robustness-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-negative-TC-HOME--f0b30-ge-—-interaction-robustness-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-negative-TC-HOME--f0b30-ge-—-interaction-robustness-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-negative-TC-HOME--f0b30-ge-—-interaction-robustness-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-067</t>
-  </si>
-  <si>
     <t>Performance observation — initial load</t>
   </si>
   <si>
@@ -485,9 +1254,6 @@
     <t>3905</t>
   </si>
   <si>
-    <t>TC-HOME-AR-070</t>
-  </si>
-  <si>
     <t>أحدث التقنيات، بأفضل قيمة — product cards</t>
   </si>
   <si>
@@ -506,9 +1272,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--c298c-002-—-sampled-product-cards-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--c298c-002-—-sampled-product-cards-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--c298c-002-—-sampled-product-cards-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--c298c-002-—-sampled-product-cards-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-074</t>
-  </si>
-  <si>
     <t>أقوى الألعاب، وأفضل العروض — product cards</t>
   </si>
   <si>
@@ -518,9 +1281,6 @@
     <t>23078</t>
   </si>
   <si>
-    <t>TC-HOME-AR-078</t>
-  </si>
-  <si>
     <t>ارتق إلى آيفون 18 — product cards</t>
   </si>
   <si>
@@ -530,9 +1290,6 @@
     <t>23303</t>
   </si>
   <si>
-    <t>TC-HOME-AR-082</t>
-  </si>
-  <si>
     <t>أناقة بسيطة، وسحر لا يقاوم. — product cards</t>
   </si>
   <si>
@@ -551,9 +1308,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--1e960-005-—-sampled-product-cards-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--1e960-005-—-sampled-product-cards-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--1e960-005-—-sampled-product-cards-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--1e960-005-—-sampled-product-cards-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-024</t>
-  </si>
-  <si>
     <t>عروض الأسبوع — product cards</t>
   </si>
   <si>
@@ -563,9 +1317,6 @@
     <t>24384</t>
   </si>
   <si>
-    <t>TC-HOME-AR-028</t>
-  </si>
-  <si>
     <t>المنتجات الأكثر شعبية — product cards</t>
   </si>
   <si>
@@ -575,9 +1326,6 @@
     <t>23264</t>
   </si>
   <si>
-    <t>TC-HOME-AR-040</t>
-  </si>
-  <si>
     <t>منتجات على ذوقك — product cards</t>
   </si>
   <si>
@@ -596,9 +1344,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--a46fe-011-—-sampled-product-cards-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--a46fe-011-—-sampled-product-cards-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--a46fe-011-—-sampled-product-cards-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-products-TC-HOME--a46fe-011-—-sampled-product-cards-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-044</t>
-  </si>
-  <si>
     <t>منتجات مناسبة لكل عمر — product cards</t>
   </si>
   <si>
@@ -608,9 +1353,6 @@
     <t>22945</t>
   </si>
   <si>
-    <t>TC-HOME-AR-053</t>
-  </si>
-  <si>
     <t>Responsive — Desktop 1440x900</t>
   </si>
   <si>
@@ -620,9 +1362,6 @@
     <t>5988</t>
   </si>
   <si>
-    <t>TC-HOME-AR-054</t>
-  </si>
-  <si>
     <t>Responsive — Desktop 1920x1080</t>
   </si>
   <si>
@@ -632,9 +1371,6 @@
     <t>8424</t>
   </si>
   <si>
-    <t>TC-HOME-AR-055</t>
-  </si>
-  <si>
     <t>Responsive — Tablet 1024x768</t>
   </si>
   <si>
@@ -644,9 +1380,6 @@
     <t>6962</t>
   </si>
   <si>
-    <t>TC-HOME-AR-056</t>
-  </si>
-  <si>
     <t>Responsive — Tablet 768x1024</t>
   </si>
   <si>
@@ -656,9 +1389,6 @@
     <t>6876</t>
   </si>
   <si>
-    <t>TC-HOME-AR-057</t>
-  </si>
-  <si>
     <t>Responsive — Mobile 390x844</t>
   </si>
   <si>
@@ -668,9 +1398,6 @@
     <t>6033</t>
   </si>
   <si>
-    <t>TC-HOME-AR-058</t>
-  </si>
-  <si>
     <t>Responsive — Mobile 393x852</t>
   </si>
   <si>
@@ -680,9 +1407,6 @@
     <t>6183</t>
   </si>
   <si>
-    <t>TC-HOME-AR-059</t>
-  </si>
-  <si>
     <t>Responsive — Mobile 412x915</t>
   </si>
   <si>
@@ -692,9 +1416,6 @@
     <t>5034</t>
   </si>
   <si>
-    <t>TC-HOME-AR-003</t>
-  </si>
-  <si>
     <t>تسوّّق حسب الماركة — carousel</t>
   </si>
   <si>
@@ -725,9 +1446,6 @@
     <t>13059</t>
   </si>
   <si>
-    <t>TC-HOME-AR-063</t>
-  </si>
-  <si>
     <t>Accessibility — keyboard &amp; names</t>
   </si>
   <si>
@@ -737,9 +1455,6 @@
     <t>7105</t>
   </si>
   <si>
-    <t>TC-HOME-AR-066</t>
-  </si>
-  <si>
     <t>Localization — switch to English</t>
   </si>
   <si>
@@ -758,9 +1473,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-066-219e1-ization-—-switch-to-English-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-066-219e1-ization-—-switch-to-English-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-066-219e1-ization-—-switch-to-English-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-066-219e1-ization-—-switch-to-English-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-065</t>
-  </si>
-  <si>
     <t>Console &amp; network health</t>
   </si>
   <si>
@@ -779,9 +1491,6 @@
     <t>C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-065-2bb36-k-health-—-first-party-only-chromium\test-failed-1.png; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-065-2bb36-k-health-—-first-party-only-chromium\video.webm; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-065-2bb36-k-health-—-first-party-only-chromium\error-context.md; C:\Users\ThinkPad T480s Pro\Documents\homepage-ts-port\test-results\homepage-ui-TC-HOME-AR-065-2bb36-k-health-—-first-party-only-chromium\trace.zip</t>
   </si>
   <si>
-    <t>TC-HOME-AR-005</t>
-  </si>
-  <si>
     <t>تسوّّق حسب الماركة — inputs</t>
   </si>
   <si>
@@ -789,9 +1498,6 @@
   </si>
   <si>
     <t>8157</t>
-  </si>
-  <si>
-    <t>TC-HOME-AR-052</t>
   </si>
   <si>
     <t>تسوق حسب الفئة — inputs</t>
@@ -987,7 +1693,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -999,8 +1705,15 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1014,12 +1727,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1035,11 +1758,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1490,6 +2228,1465 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="105" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" ht="75" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" ht="105" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" ht="105" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" ht="105" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+    </row>
+    <row r="61" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+    </row>
+    <row r="69" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" ht="120" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" ht="60" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A72:G72"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1511,13 +3708,13 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -1526,42 +3723,42 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>272</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1572,23 +3769,23 @@
       <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>272</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="M2" t="s">
         <v>15</v>
@@ -1599,13 +3796,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1616,23 +3813,23 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>276</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>277</v>
       </c>
       <c r="M3" t="s">
         <v>15</v>
@@ -1643,13 +3840,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1660,23 +3857,23 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>279</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K4" t="s">
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="M4" t="s">
         <v>15</v>
@@ -1687,13 +3884,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -1704,23 +3901,23 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K5" t="s">
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
       <c r="M5" t="s">
         <v>15</v>
@@ -1731,13 +3928,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1748,23 +3945,23 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="M6" t="s">
         <v>15</v>
@@ -1775,13 +3972,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>287</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -1792,23 +3989,23 @@
       <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>289</v>
       </c>
       <c r="M7" t="s">
         <v>15</v>
@@ -1819,13 +4016,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>291</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1836,23 +4033,23 @@
       <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>291</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>58</v>
+        <v>292</v>
       </c>
       <c r="M8" t="s">
         <v>15</v>
@@ -1863,13 +4060,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1880,23 +4077,23 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>294</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>295</v>
       </c>
       <c r="M9" t="s">
         <v>15</v>
@@ -1907,13 +4104,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1924,23 +4121,23 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="M10" t="s">
         <v>15</v>
@@ -1951,13 +4148,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1968,23 +4165,23 @@
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>70</v>
+        <v>301</v>
       </c>
       <c r="M11" t="s">
         <v>15</v>
@@ -1995,13 +4192,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>302</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>303</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -2012,23 +4209,23 @@
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>303</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>74</v>
+        <v>304</v>
       </c>
       <c r="M12" t="s">
         <v>15</v>
@@ -2039,13 +4236,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -2056,23 +4253,23 @@
       <c r="F13" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -2083,13 +4280,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -2100,23 +4297,23 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="J14" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="M14" t="s">
         <v>15</v>
@@ -2127,13 +4324,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -2144,23 +4341,23 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>313</v>
       </c>
       <c r="M15" t="s">
         <v>15</v>
@@ -2171,13 +4368,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>314</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -2188,26 +4385,26 @@
       <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
       <c r="J16" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>317</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="N16" t="s">
         <v>15</v>
@@ -2215,13 +4412,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>319</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>320</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -2232,23 +4429,23 @@
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>320</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="M17" t="s">
         <v>15</v>
@@ -2259,13 +4456,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -2276,23 +4473,23 @@
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="J18" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="M18" t="s">
         <v>15</v>
@@ -2303,13 +4500,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
@@ -2320,23 +4517,23 @@
       <c r="F19" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>327</v>
       </c>
       <c r="M19" t="s">
         <v>15</v>
@@ -2347,13 +4544,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -2364,23 +4561,23 @@
       <c r="F20" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>106</v>
+        <v>329</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>107</v>
+        <v>330</v>
       </c>
       <c r="M20" t="s">
         <v>15</v>
@@ -2391,13 +4588,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -2408,23 +4605,23 @@
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="J21" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="M21" t="s">
         <v>15</v>
@@ -2435,13 +4632,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>334</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -2452,23 +4649,23 @@
       <c r="F22" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>114</v>
+        <v>335</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>115</v>
+        <v>336</v>
       </c>
       <c r="M22" t="s">
         <v>15</v>
@@ -2479,13 +4676,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>338</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -2496,23 +4693,23 @@
       <c r="F23" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>118</v>
+        <v>338</v>
       </c>
       <c r="J23" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>119</v>
+        <v>339</v>
       </c>
       <c r="M23" t="s">
         <v>15</v>
@@ -2523,13 +4720,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>340</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>341</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
@@ -2540,23 +4737,23 @@
       <c r="F24" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>341</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>123</v>
+        <v>342</v>
       </c>
       <c r="M24" t="s">
         <v>15</v>
@@ -2567,13 +4764,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>344</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
@@ -2584,23 +4781,23 @@
       <c r="F25" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>126</v>
+        <v>344</v>
       </c>
       <c r="J25" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>127</v>
+        <v>345</v>
       </c>
       <c r="M25" t="s">
         <v>15</v>
@@ -2611,13 +4808,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>346</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>347</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
@@ -2628,23 +4825,23 @@
       <c r="F26" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>130</v>
+        <v>347</v>
       </c>
       <c r="J26" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>131</v>
+        <v>348</v>
       </c>
       <c r="M26" t="s">
         <v>15</v>
@@ -2655,13 +4852,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>350</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -2672,23 +4869,23 @@
       <c r="F27" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>134</v>
+        <v>350</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K27" t="s">
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>135</v>
+        <v>351</v>
       </c>
       <c r="M27" t="s">
         <v>15</v>
@@ -2699,13 +4896,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>352</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -2716,23 +4913,23 @@
       <c r="F28" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="J28" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K28" t="s">
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>139</v>
+        <v>354</v>
       </c>
       <c r="M28" t="s">
         <v>15</v>
@@ -2743,13 +4940,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>355</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>356</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -2760,26 +4957,26 @@
       <c r="F29" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>142</v>
+        <v>356</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="K29" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="L29" t="s">
-        <v>143</v>
+        <v>357</v>
       </c>
       <c r="M29" t="s">
-        <v>144</v>
+        <v>358</v>
       </c>
       <c r="N29" t="s">
         <v>15</v>
@@ -2787,13 +4984,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>359</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -2804,26 +5001,26 @@
       <c r="F30" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="J30" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="K30" t="s">
-        <v>149</v>
+        <v>362</v>
       </c>
       <c r="L30" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>364</v>
       </c>
       <c r="N30" t="s">
         <v>15</v>
@@ -2831,13 +5028,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>365</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>366</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -2848,23 +5045,23 @@
       <c r="F31" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>154</v>
+        <v>366</v>
       </c>
       <c r="J31" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>155</v>
+        <v>367</v>
       </c>
       <c r="M31" t="s">
         <v>15</v>
@@ -2875,13 +5072,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>368</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>369</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -2892,26 +5089,26 @@
       <c r="F32" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>369</v>
       </c>
       <c r="J32" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K32" t="s">
-        <v>160</v>
+        <v>371</v>
       </c>
       <c r="L32" t="s">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="M32" t="s">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="N32" t="s">
         <v>15</v>
@@ -2919,13 +5116,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>375</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -2936,23 +5133,23 @@
       <c r="F33" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>165</v>
+        <v>375</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>166</v>
+        <v>376</v>
       </c>
       <c r="M33" t="s">
         <v>15</v>
@@ -2963,13 +5160,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>377</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>378</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -2980,23 +5177,23 @@
       <c r="F34" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>169</v>
+        <v>378</v>
       </c>
       <c r="J34" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K34" t="s">
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>170</v>
+        <v>379</v>
       </c>
       <c r="M34" t="s">
         <v>15</v>
@@ -3007,13 +5204,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>380</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -3024,26 +5221,26 @@
       <c r="F35" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="J35" t="s">
-        <v>174</v>
+        <v>382</v>
       </c>
       <c r="K35" t="s">
-        <v>175</v>
+        <v>383</v>
       </c>
       <c r="L35" t="s">
-        <v>176</v>
+        <v>384</v>
       </c>
       <c r="M35" t="s">
-        <v>177</v>
+        <v>385</v>
       </c>
       <c r="N35" t="s">
         <v>15</v>
@@ -3051,13 +5248,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -3068,23 +5265,23 @@
       <c r="F36" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="M36" t="s">
         <v>15</v>
@@ -3095,13 +5292,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>389</v>
       </c>
       <c r="C37" t="s">
-        <v>184</v>
+        <v>390</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
@@ -3112,23 +5309,23 @@
       <c r="F37" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>390</v>
       </c>
       <c r="J37" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>185</v>
+        <v>391</v>
       </c>
       <c r="M37" t="s">
         <v>15</v>
@@ -3139,13 +5336,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>392</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>393</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -3156,26 +5353,26 @@
       <c r="F38" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>188</v>
+        <v>393</v>
       </c>
       <c r="J38" t="s">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="K38" t="s">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L38" t="s">
-        <v>191</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s">
-        <v>192</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s">
         <v>15</v>
@@ -3183,13 +5380,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>398</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -3200,23 +5397,23 @@
       <c r="F39" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="J39" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>196</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s">
         <v>15</v>
@@ -3227,13 +5424,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>401</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>402</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
@@ -3244,23 +5441,23 @@
       <c r="F40" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>199</v>
+        <v>402</v>
       </c>
       <c r="J40" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s">
         <v>15</v>
@@ -3271,13 +5468,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>404</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -3288,23 +5485,23 @@
       <c r="F41" t="s">
         <v>16</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s">
         <v>15</v>
@@ -3315,13 +5512,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>407</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>408</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -3332,23 +5529,23 @@
       <c r="F42" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>207</v>
+        <v>408</v>
       </c>
       <c r="J42" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K42" t="s">
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s">
         <v>15</v>
@@ -3359,13 +5556,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>211</v>
+        <v>411</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -3376,23 +5573,23 @@
       <c r="F43" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>211</v>
+        <v>411</v>
       </c>
       <c r="J43" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>212</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s">
         <v>15</v>
@@ -3403,13 +5600,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>413</v>
       </c>
       <c r="C44" t="s">
-        <v>215</v>
+        <v>414</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -3420,23 +5617,23 @@
       <c r="F44" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>215</v>
+        <v>414</v>
       </c>
       <c r="J44" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="M44" t="s">
         <v>15</v>
@@ -3447,13 +5644,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>218</v>
+        <v>416</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>417</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -3464,23 +5661,23 @@
       <c r="F45" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>219</v>
+        <v>417</v>
       </c>
       <c r="J45" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>220</v>
+        <v>418</v>
       </c>
       <c r="M45" t="s">
         <v>15</v>
@@ -3491,13 +5688,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="C46" t="s">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -3508,23 +5705,23 @@
       <c r="F46" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="J46" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>224</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s">
         <v>15</v>
@@ -3535,13 +5732,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>422</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>423</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -3552,26 +5749,26 @@
       <c r="F47" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>227</v>
+        <v>423</v>
       </c>
       <c r="J47" t="s">
-        <v>228</v>
+        <v>424</v>
       </c>
       <c r="K47" t="s">
-        <v>229</v>
+        <v>425</v>
       </c>
       <c r="L47" t="s">
-        <v>230</v>
+        <v>426</v>
       </c>
       <c r="M47" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="N47" t="s">
         <v>15</v>
@@ -3579,13 +5776,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>428</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>430</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -3596,23 +5793,23 @@
       <c r="F48" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>234</v>
+        <v>430</v>
       </c>
       <c r="J48" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K48" t="s">
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>235</v>
+        <v>431</v>
       </c>
       <c r="M48" t="s">
         <v>15</v>
@@ -3623,13 +5820,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
-        <v>237</v>
+        <v>432</v>
       </c>
       <c r="C49" t="s">
-        <v>238</v>
+        <v>433</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -3640,23 +5837,23 @@
       <c r="F49" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>238</v>
+        <v>433</v>
       </c>
       <c r="J49" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>239</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s">
         <v>15</v>
@@ -3667,13 +5864,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>241</v>
+        <v>435</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>436</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -3684,26 +5881,26 @@
       <c r="F50" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>242</v>
+        <v>436</v>
       </c>
       <c r="J50" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="K50" t="s">
-        <v>244</v>
+        <v>438</v>
       </c>
       <c r="L50" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="N50" t="s">
         <v>15</v>
@@ -3711,13 +5908,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="B51" t="s">
-        <v>248</v>
+        <v>441</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -3728,26 +5925,26 @@
       <c r="F51" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
       </c>
       <c r="I51" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
       <c r="J51" t="s">
-        <v>250</v>
+        <v>443</v>
       </c>
       <c r="K51" t="s">
-        <v>251</v>
+        <v>444</v>
       </c>
       <c r="L51" t="s">
-        <v>252</v>
+        <v>445</v>
       </c>
       <c r="M51" t="s">
-        <v>253</v>
+        <v>446</v>
       </c>
       <c r="N51" t="s">
         <v>15</v>
@@ -3755,13 +5952,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>254</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>447</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>448</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -3772,23 +5969,23 @@
       <c r="F52" t="s">
         <v>16</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>256</v>
+        <v>448</v>
       </c>
       <c r="J52" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>257</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s">
         <v>15</v>
@@ -3799,13 +5996,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>258</v>
+        <v>139</v>
       </c>
       <c r="B53" t="s">
-        <v>259</v>
+        <v>450</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -3816,23 +6013,23 @@
       <c r="F53" t="s">
         <v>16</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="J53" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>261</v>
+        <v>452</v>
       </c>
       <c r="M53" t="s">
         <v>15</v>
@@ -3848,7 +6045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3871,13 +6068,13 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3886,42 +6083,42 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>314</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -3932,26 +6129,26 @@
       <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
       <c r="J2" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="L2" t="s">
-        <v>90</v>
+        <v>317</v>
       </c>
       <c r="M2" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="N2" t="s">
         <v>15</v>
@@ -3959,13 +6156,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>355</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -3976,26 +6173,26 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>142</v>
+        <v>356</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="L3" t="s">
-        <v>143</v>
+        <v>357</v>
       </c>
       <c r="M3" t="s">
-        <v>144</v>
+        <v>358</v>
       </c>
       <c r="N3" t="s">
         <v>15</v>
@@ -4003,13 +6200,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -4020,26 +6217,26 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="J4" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>362</v>
       </c>
       <c r="L4" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="M4" t="s">
-        <v>151</v>
+        <v>364</v>
       </c>
       <c r="N4" t="s">
         <v>15</v>
@@ -4047,13 +6244,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>368</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>369</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -4064,26 +6261,26 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>158</v>
+        <v>369</v>
       </c>
       <c r="J5" t="s">
-        <v>159</v>
+        <v>370</v>
       </c>
       <c r="K5" t="s">
-        <v>160</v>
+        <v>371</v>
       </c>
       <c r="L5" t="s">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="M5" t="s">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="N5" t="s">
         <v>15</v>
@@ -4091,13 +6288,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -4108,26 +6305,26 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="J6" t="s">
-        <v>174</v>
+        <v>382</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>383</v>
       </c>
       <c r="L6" t="s">
-        <v>176</v>
+        <v>384</v>
       </c>
       <c r="M6" t="s">
-        <v>177</v>
+        <v>385</v>
       </c>
       <c r="N6" t="s">
         <v>15</v>
@@ -4135,13 +6332,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>393</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -4152,26 +6349,26 @@
       <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>188</v>
+        <v>393</v>
       </c>
       <c r="J7" t="s">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="K7" t="s">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L7" t="s">
-        <v>191</v>
+        <v>396</v>
       </c>
       <c r="M7" t="s">
-        <v>192</v>
+        <v>397</v>
       </c>
       <c r="N7" t="s">
         <v>15</v>
@@ -4179,13 +6376,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>422</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>423</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -4196,26 +6393,26 @@
       <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>227</v>
+        <v>423</v>
       </c>
       <c r="J8" t="s">
-        <v>228</v>
+        <v>424</v>
       </c>
       <c r="K8" t="s">
-        <v>229</v>
+        <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>230</v>
+        <v>426</v>
       </c>
       <c r="M8" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="N8" t="s">
         <v>15</v>
@@ -4223,13 +6420,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>435</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>436</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -4240,26 +6437,26 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>242</v>
+        <v>436</v>
       </c>
       <c r="J9" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="K9" t="s">
-        <v>244</v>
+        <v>438</v>
       </c>
       <c r="L9" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="M9" t="s">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="N9" t="s">
         <v>15</v>
@@ -4267,13 +6464,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>441</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -4284,26 +6481,26 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
       <c r="J10" t="s">
-        <v>250</v>
+        <v>443</v>
       </c>
       <c r="K10" t="s">
-        <v>251</v>
+        <v>444</v>
       </c>
       <c r="L10" t="s">
-        <v>252</v>
+        <v>445</v>
       </c>
       <c r="M10" t="s">
-        <v>253</v>
+        <v>446</v>
       </c>
       <c r="N10" t="s">
         <v>15</v>
@@ -4316,7 +6513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4328,211 +6525,211 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>453</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>454</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>457</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>459</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>460</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>461</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>462</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>464</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>465</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B10" t="s">
-        <v>276</v>
+        <v>467</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>469</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>470</v>
       </c>
       <c r="C12" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>471</v>
       </c>
       <c r="C13" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B14" t="s">
-        <v>281</v>
+        <v>472</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>473</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="B16" t="s">
-        <v>283</v>
+        <v>474</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>284</v>
+        <v>475</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>476</v>
       </c>
       <c r="C17" t="s">
-        <v>286</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>475</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>478</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>284</v>
+        <v>475</v>
       </c>
       <c r="B19" t="s">
-        <v>289</v>
+        <v>480</v>
       </c>
       <c r="C19" t="s">
-        <v>290</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -4541,7 +6738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4553,409 +6750,409 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>291</v>
+        <v>482</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>483</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>368</v>
       </c>
       <c r="C4" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B5" t="s">
-        <v>295</v>
+        <v>486</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>487</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>325</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>377</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>488</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>380</v>
       </c>
       <c r="C16" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>489</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>491</v>
       </c>
       <c r="C19" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>493</v>
       </c>
       <c r="C20" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B21" t="s">
-        <v>303</v>
+        <v>494</v>
       </c>
       <c r="C21" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B22" t="s">
-        <v>304</v>
+        <v>495</v>
       </c>
       <c r="C22" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B23" t="s">
-        <v>305</v>
+        <v>496</v>
       </c>
       <c r="C23" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B25" t="s">
-        <v>307</v>
+        <v>498</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B26" t="s">
-        <v>308</v>
+        <v>499</v>
       </c>
       <c r="C26" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B27" t="s">
-        <v>309</v>
+        <v>500</v>
       </c>
       <c r="C27" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B28" t="s">
-        <v>310</v>
+        <v>501</v>
       </c>
       <c r="C28" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B29" t="s">
-        <v>311</v>
+        <v>502</v>
       </c>
       <c r="C29" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B30" t="s">
-        <v>312</v>
+        <v>503</v>
       </c>
       <c r="C30" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B31" t="s">
-        <v>313</v>
+        <v>504</v>
       </c>
       <c r="C31" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>505</v>
       </c>
       <c r="C32" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B33" t="s">
-        <v>315</v>
+        <v>506</v>
       </c>
       <c r="C33" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B34" t="s">
-        <v>316</v>
+        <v>507</v>
       </c>
       <c r="C34" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B35" t="s">
-        <v>317</v>
+        <v>508</v>
       </c>
       <c r="C35" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B36" t="s">
-        <v>318</v>
+        <v>509</v>
       </c>
       <c r="C36" t="s">
-        <v>301</v>
+        <v>492</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>319</v>
+        <v>510</v>
       </c>
       <c r="B37" t="s">
-        <v>320</v>
+        <v>511</v>
       </c>
       <c r="C37" t="s">
-        <v>321</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
